--- a/growth-hub/puanlama/Mecra_Karnesi.xlsx
+++ b/growth-hub/puanlama/Mecra_Karnesi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mecra Karnesi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mecra Karnesi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mecra Karnesi'!$A$1:$R$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mecra Karnesi'!$A$1:$U$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,27 +452,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:U93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,70 +501,85 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Reklam modeli</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Örnek yayın türü</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Fiyat Tipi</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Puan</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fayda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Puan aralığı</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Kaç satır</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Kaç kampanya</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ortalama yayınlanma %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Önerilen birim maliyet</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Öneri neye dayanıyor</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Kaç gözlemden</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Toplam harcama</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Puan nereden geliyor</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Karşılaştırma havuzu</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Son kampanya</t>
         </is>
@@ -590,56 +608,69 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video - Atlanamayan</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>108.3</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>32–184</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>0.1903</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -668,56 +699,69 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Non Skippable</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>30–182</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>67.6767</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="4" t="n">
         <v>297519</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -746,56 +790,69 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video - Atlanamayan</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>105.7</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>30–182</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>0.2144</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -824,56 +881,69 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video - Atlanamayan</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>105.4</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>29–181</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>0.2183</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -902,56 +972,69 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video - Atlanamayan</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>100.5</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>0.2901</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -980,56 +1063,69 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video - Atlanamayan</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>94.5</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>37–152</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>0.3863</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1058,56 +1154,69 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video - Atlanamayan</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>90.2</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>32–148</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>0.7446</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>220000</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1136,56 +1245,69 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>CTV</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>Connected Tv</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>100.9</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>25–177</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>103.2524</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>26244</v>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -1214,56 +1336,69 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>8.005699999999999</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>206547</v>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -1292,56 +1427,69 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>Video view</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>0.0202</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>247275</v>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1370,56 +1518,69 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>112.8</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>63–163</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="M12" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>29.8072</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>589486</v>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -1448,56 +1609,69 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Trueview in-stream</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>100.5</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>43–158</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="n">
+      <c r="L13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="N13" s="3" t="n">
         <v>0.1719</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>872539</v>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1526,56 +1700,69 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Video View</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="N14" s="3" t="n">
         <v>0.1746</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="4" t="n">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>199302</v>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1604,56 +1791,69 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Trueview for Action</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>89.3</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>13–165</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="N15" s="3" t="n">
         <v>119.5787</v>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="4" t="n">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>37055</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1682,56 +1882,69 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Video view - Thruplay</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>83.8</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>34–134</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="n">
+      <c r="L16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="N16" s="3" t="n">
         <v>0.3341</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>666088</v>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1765,51 +1978,64 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Masthead</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="N17" s="3" t="n">
         <v>8.9315</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="4" t="n">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>134000</v>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1838,56 +2064,69 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Preroll Video</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="N18" s="3" t="n">
         <v>0.058</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>177255</v>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -1921,51 +2160,64 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>100.9</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>25–177</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="N19" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="4" t="n">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>43965</v>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -1999,51 +2251,64 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="N20" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="4" t="n">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>14735</v>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2077,51 +2342,64 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="N21" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="4" t="n">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>30944</v>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2155,51 +2433,64 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="N22" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="4" t="n">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>23762</v>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2233,51 +2524,64 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="N23" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="4" t="n">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>24427</v>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2311,51 +2615,64 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>91.5</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>16–168</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="N24" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="4" t="n">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>30778</v>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2389,51 +2706,64 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>91.5</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>16–168</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="N25" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="4" t="n">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>129365</v>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2462,56 +2792,69 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>Ses</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Audio</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="N26" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="4" t="n">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>40011</v>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2540,56 +2883,69 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>First View + Spotlight Trend Takeover</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="N27" s="3" t="n">
         <v>0.0722</v>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" s="4" t="n">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="4" t="n">
         <v>179553</v>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -2618,56 +2974,69 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Spoonsor Ürün</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>14–166</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="N28" s="3" t="n">
         <v>1.2045</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" s="4" t="n">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="4" t="n">
         <v>1290</v>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2696,56 +3065,69 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Traffic</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>72–188</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="L29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="M29" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="N29" s="3" t="n">
         <v>0.155</v>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>134239</v>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2774,56 +3156,69 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>Traffic</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="N30" s="3" t="n">
         <v>1.4708</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="4" t="n">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="4" t="n">
         <v>158363</v>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -2852,56 +3247,69 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>Banner CPC</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>13–165</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="N31" s="3" t="n">
         <v>9.1213</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="4" t="n">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="4" t="n">
         <v>33986</v>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -2930,56 +3338,69 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>Traffic</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>88.2</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>38–138</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="K32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="L32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="M32" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="N32" s="3" t="n">
         <v>2.7203</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>225155</v>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -3008,56 +3429,69 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Oyun içi</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Attention Accelerator</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>104.7</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>29–181</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="N33" s="3" t="n">
         <v>0.2499</v>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="4" t="n">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="4" t="n">
         <v>270000</v>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3086,56 +3520,69 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Oyun içi</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Oyun içi Rich Media</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>95.3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>19–171</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="N34" s="3" t="n">
         <v>0.4964</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" s="4" t="n">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3169,51 +3616,64 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="N35" s="3" t="n">
         <v>0.0347</v>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="4" t="n">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="4" t="n">
         <v>250000</v>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -3247,51 +3707,64 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="N36" s="3" t="n">
         <v>0.0956</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="4" t="n">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="4" t="n">
         <v>250000</v>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -3325,51 +3798,64 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>110.4</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>34–186</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="N37" s="3" t="n">
         <v>0.2433</v>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" s="4" t="n">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="4" t="n">
         <v>350000</v>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -3403,51 +3889,64 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>104.9</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>29–181</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="N38" s="3" t="n">
         <v>0.3129</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" s="4" t="n">
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="4" t="n">
         <v>472500</v>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -3481,51 +3980,64 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>103.1</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>45–161</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="2" t="n">
+      <c r="L39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="N39" s="3" t="n">
         <v>0.3738</v>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="Q39" s="4" t="n">
         <v>400000</v>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3559,51 +4071,64 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>102.2</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>26–178</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="N40" s="3" t="n">
         <v>0.3644</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" s="4" t="n">
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3637,51 +4162,64 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="N41" s="3" t="n">
         <v>0.4209</v>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" s="4" t="n">
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3715,51 +4253,64 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>98.2</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>22–174</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="N42" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" s="4" t="n">
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="4" t="n">
         <v>224399</v>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -3793,51 +4344,64 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>97.2</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>21–173</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="N43" s="3" t="n">
         <v>0.5219</v>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" s="4" t="n">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="4" t="n">
         <v>220000</v>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3871,51 +4435,64 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>21–173</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="N44" s="3" t="n">
         <v>0.5266999999999999</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" s="4" t="n">
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -3944,56 +4521,69 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>Preroll &amp; Liveroll</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>38–154</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="N45" s="3" t="n">
         <v>0.5131</v>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n">
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O45" s="4" t="n">
+      <c r="Q45" s="4" t="n">
         <v>375000</v>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -4027,51 +4617,64 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>93.8</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>36–152</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="N46" s="3" t="n">
         <v>0.5669</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n">
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O46" s="4" t="n">
+      <c r="Q46" s="4" t="n">
         <v>280910</v>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -4105,51 +4708,64 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>87.3</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>30–145</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="K47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="L47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="M47" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="N47" s="3" t="n">
         <v>0.9664</v>
       </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n">
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="Q47" s="4" t="n">
         <v>582287</v>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -4178,56 +4794,69 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Video Endcard + BLS</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>106.4</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>30–182</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="N48" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" s="4" t="n">
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="4" t="n">
         <v>131037</v>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -4256,56 +4885,69 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>Partner Sales</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="L49" s="3" t="n">
+      <c r="N49" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="4" t="n">
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="4" t="n">
         <v>144960</v>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -4334,56 +4976,69 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>Alt Bant</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="H50" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>22–174</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="L50" s="3" t="n">
+      <c r="N50" s="3" t="n">
         <v>0.4867</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" s="4" t="n">
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="4" t="n">
         <v>80000</v>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
@@ -4412,56 +5067,69 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>Arama</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>106.4</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>30–182</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="N51" s="3" t="n">
         <v>2.6363</v>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" s="4" t="n">
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="4" t="n">
         <v>71258</v>
       </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4490,56 +5158,69 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>Non-skippable</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>16–168</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="L52" s="3" t="n">
+      <c r="N52" s="3" t="n">
         <v>220.0953</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="4" t="n">
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="4" t="n">
         <v>384037</v>
       </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4568,56 +5249,69 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
+          <t>CTV</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>Connected Tv</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>18–170</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L53" s="3" t="n">
+      <c r="N53" s="3" t="n">
         <v>199.1825</v>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="4" t="n">
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="4" t="n">
         <v>64847</v>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4646,56 +5340,69 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>Video View</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>110.6</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>35–187</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="L54" s="3" t="n">
+      <c r="N54" s="3" t="n">
         <v>0.1007</v>
       </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" s="4" t="n">
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="4" t="n">
         <v>31108</v>
       </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4724,56 +5431,69 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>104.3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>28–180</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="L55" s="3" t="n">
+      <c r="N55" s="3" t="n">
         <v>0.1343</v>
       </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" s="4" t="n">
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="4" t="n">
         <v>30675</v>
       </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4802,56 +5522,69 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>Oyun içi</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>In - Game Video</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>105.5</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>30–182</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="N56" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" s="4" t="n">
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="4" t="n">
         <v>21886</v>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4885,51 +5618,64 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>102.1</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>26–178</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="L57" s="3" t="n">
+      <c r="N57" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" s="4" t="n">
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="4" t="n">
         <v>79176</v>
       </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -4963,51 +5709,64 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="H58" s="2" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>21–173</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="L58" s="3" t="n">
+      <c r="N58" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" s="4" t="n">
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="4" t="n">
         <v>96106</v>
       </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -5036,56 +5795,69 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>Traffc</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L59" s="3" t="n">
+      <c r="N59" s="3" t="n">
         <v>0.1001</v>
       </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="4" t="n">
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="4" t="n">
         <v>39334</v>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -5114,56 +5886,69 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>Traffic</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>100.4</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="L60" s="3" t="n">
+      <c r="N60" s="3" t="n">
         <v>3.4109</v>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="4" t="n">
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="4" t="n">
         <v>121389</v>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -5192,56 +5977,69 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>Big &amp; Bold Banner CPC</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="H61" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="L61" s="3" t="n">
+      <c r="N61" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="4" t="n">
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="4" t="n">
         <v>38269</v>
       </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -5270,56 +6068,69 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>Display CPC</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>98.2</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>22–174</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="N62" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="4" t="n">
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="4" t="n">
         <v>40760</v>
       </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -5348,56 +6159,69 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
+          <t>Tıklama odaklı</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>Native CPC</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>98.2</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>22–174</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="L63" s="3" t="n">
+      <c r="N63" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" s="4" t="n">
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="4" t="n">
         <v>18820</v>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R63" s="2" t="inlineStr">
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
@@ -5426,56 +6250,69 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
+          <t>Arama</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>21–173</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="L64" s="3" t="n">
+      <c r="N64" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="4" t="n">
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="4" t="n">
         <v>49205</v>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5504,56 +6341,69 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
+          <t>Atlanamayan video</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>Non Skippable</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>100.4</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>43–158</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="K65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="L65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="M65" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="L65" s="3" t="n">
+      <c r="N65" s="3" t="n">
         <v>95.9447</v>
       </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="n">
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O65" s="4" t="n">
+      <c r="Q65" s="4" t="n">
         <v>1689686</v>
       </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr">
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -5582,56 +6432,69 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
+          <t>CTV</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>Connected Tv</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="H66" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L66" s="3" t="n">
+      <c r="N66" s="3" t="n">
         <v>0.09420000000000001</v>
       </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" s="4" t="n">
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R66" s="2" t="inlineStr">
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5660,56 +6523,69 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
+          <t>CTV</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>Connected Tv</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="H67" s="2" t="n">
         <v>101.8</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>44–160</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="K67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="L67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="2" t="n">
+      <c r="M67" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="L67" s="3" t="n">
+      <c r="N67" s="3" t="n">
         <v>104.1467</v>
       </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="n">
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O67" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>649709</v>
       </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5738,56 +6614,69 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
+          <t>CTV</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>Connected Tv</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="H68" s="2" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>40–155</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="K68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="L68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K68" s="2" t="n">
+      <c r="M68" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="L68" s="3" t="n">
+      <c r="N68" s="3" t="n">
         <v>0.3148</v>
       </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="n">
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O68" s="4" t="n">
+      <c r="Q68" s="4" t="n">
         <v>800000</v>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R68" s="2" t="inlineStr">
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5816,56 +6705,69 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="H69" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="L69" s="3" t="n">
+      <c r="N69" s="3" t="n">
         <v>19.6108</v>
       </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" s="4" t="n">
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R69" s="2" t="inlineStr">
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5894,56 +6796,69 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L70" s="3" t="n">
+      <c r="N70" s="3" t="n">
         <v>0.09420000000000001</v>
       </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" s="4" t="n">
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R70" s="2" t="inlineStr">
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5972,56 +6887,69 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="H71" s="2" t="n">
         <v>107.8</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="n">
+        <v>323.4</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>32–184</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L71" s="3" t="n">
+      <c r="N71" s="3" t="n">
         <v>0.1414</v>
       </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" s="4" t="n">
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="4" t="n">
         <v>150000</v>
       </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr">
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6050,56 +6978,69 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="H72" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="L72" s="3" t="n">
+      <c r="N72" s="3" t="n">
         <v>0.2243</v>
       </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" s="4" t="n">
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="4" t="n">
         <v>46794</v>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R72" s="2" t="inlineStr">
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6128,56 +7069,69 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>Truview</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>49–149</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="K73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="L73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="M73" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="L73" s="3" t="n">
+      <c r="N73" s="3" t="n">
         <v>0.2312</v>
       </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="n">
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O73" s="4" t="n">
+      <c r="Q73" s="4" t="n">
         <v>1199573</v>
       </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr">
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6206,56 +7160,69 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>Trivuew</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="H74" s="2" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>20–172</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="L74" s="3" t="n">
+      <c r="N74" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" s="4" t="n">
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="4" t="n">
         <v>270263</v>
       </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr">
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6284,56 +7251,69 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>Video Views</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="H75" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>57–129</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="K75" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="L75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="M75" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="L75" s="3" t="n">
+      <c r="N75" s="3" t="n">
         <v>55.9144</v>
       </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="n">
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="O75" s="4" t="n">
+      <c r="Q75" s="4" t="n">
         <v>2814774</v>
       </c>
-      <c r="P75" s="2" t="inlineStr">
+      <c r="R75" s="2" t="inlineStr">
         <is>
           <t>kendi verisi</t>
         </is>
       </c>
-      <c r="Q75" s="2" t="inlineStr">
+      <c r="S75" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr">
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6362,56 +7342,69 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
+          <t>Kısa video</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" s="2" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>13–165</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="L76" s="3" t="n">
+      <c r="N76" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" s="4" t="n">
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="4" t="n">
         <v>126373</v>
       </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6445,51 +7438,64 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
+          <t>Masthead</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="H77" s="2" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>18–170</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="L77" s="3" t="n">
+      <c r="N77" s="3" t="n">
         <v>41.9795</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" s="4" t="n">
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="4" t="n">
         <v>625899</v>
       </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr">
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6518,56 +7524,69 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
+          <t>Oyun içi</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>Preroll + Rich Media</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="H78" s="2" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>21–173</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="L78" s="3" t="n">
+      <c r="N78" s="3" t="n">
         <v>0.4158</v>
       </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" s="4" t="n">
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="4" t="n">
         <v>250000</v>
       </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R78" s="2" t="inlineStr">
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6601,51 +7620,64 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="H79" s="2" t="n">
         <v>117.1</v>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>41–193</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="L79" s="3" t="n">
+      <c r="N79" s="3" t="n">
         <v>6.9577</v>
       </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" s="4" t="n">
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr">
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6679,51 +7711,64 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="H80" s="2" t="n">
         <v>104.9</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>29–181</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="L80" s="3" t="n">
+      <c r="N80" s="3" t="n">
         <v>0.4469</v>
       </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" s="4" t="n">
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr">
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6757,51 +7802,64 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="H81" s="2" t="n">
         <v>103.3</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>27–179</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="L81" s="3" t="n">
+      <c r="N81" s="3" t="n">
         <v>0.4875</v>
       </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" s="4" t="n">
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="4" t="n">
         <v>400000</v>
       </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R81" s="2" t="inlineStr">
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6835,51 +7893,64 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="H82" s="2" t="n">
         <v>100.1</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="L82" s="3" t="n">
+      <c r="N82" s="3" t="n">
         <v>0.5939</v>
       </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" s="4" t="n">
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" s="4" t="n">
         <v>250000</v>
       </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R82" s="2" t="inlineStr">
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6913,51 +7984,64 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="L83" s="3" t="n">
+      <c r="N83" s="3" t="n">
         <v>0.6046</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" s="4" t="n">
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R83" s="2" t="inlineStr">
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -6991,51 +8075,64 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>41–157</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="K84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="L84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="M84" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="L84" s="3" t="n">
+      <c r="N84" s="3" t="n">
         <v>0.6244</v>
       </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="n">
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O84" s="4" t="n">
+      <c r="Q84" s="4" t="n">
         <v>550000</v>
       </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R84" s="2" t="inlineStr">
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7069,51 +8166,64 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>40–156</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="K85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K85" s="2" t="n">
+      <c r="M85" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="L85" s="3" t="n">
+      <c r="N85" s="3" t="n">
         <v>53.782</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="n">
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O85" s="4" t="n">
+      <c r="Q85" s="4" t="n">
         <v>1099929</v>
       </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R85" s="2" t="inlineStr">
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7147,51 +8257,64 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="H86" s="2" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>15–167</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="L86" s="3" t="n">
+      <c r="N86" s="3" t="n">
         <v>1.5153</v>
       </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" s="4" t="n">
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R86" s="2" t="inlineStr">
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7225,51 +8348,64 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
+          <t>Preroll</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="H87" s="2" t="n">
         <v>90.5</v>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>14–166</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="L87" s="3" t="n">
+      <c r="N87" s="3" t="n">
         <v>1.7922</v>
       </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" s="4" t="n">
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R87" s="2" t="inlineStr">
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7298,56 +8434,69 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
+          <t>Ses</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>Audio</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="H88" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="L88" s="3" t="n">
+      <c r="N88" s="3" t="n">
         <v>0.3206</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" s="4" t="n">
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr">
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
         <is>
           <t>tüm sektörler, yayın türü</t>
         </is>
       </c>
-      <c r="R88" s="2" t="inlineStr">
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7376,56 +8525,69 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>3D Kreatör + Alt Bant</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="H89" s="2" t="n">
         <v>104.4</v>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>28–180</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="L89" s="3" t="n">
+      <c r="N89" s="3" t="n">
         <v>0.2371</v>
       </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" s="4" t="n">
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr">
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R89" s="2" t="inlineStr">
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7454,56 +8616,69 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>Reach Block - Final Four</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="H90" s="2" t="n">
         <v>100.1</v>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>42–158</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="K90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="L90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K90" s="2" t="n">
+      <c r="M90" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="L90" s="3" t="n">
+      <c r="N90" s="3" t="n">
         <v>13.6383</v>
       </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="n">
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O90" s="4" t="n">
+      <c r="Q90" s="4" t="n">
         <v>135300</v>
       </c>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="inlineStr">
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R90" s="2" t="inlineStr">
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7532,56 +8707,69 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>İnteractive endcard</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>24–176</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="L91" s="3" t="n">
+      <c r="N91" s="3" t="n">
         <v>0.3096</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O91" s="4" t="n">
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="4" t="n">
         <v>350000</v>
       </c>
-      <c r="P91" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="inlineStr">
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R91" s="2" t="inlineStr">
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7610,56 +8798,69 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>Video End Card + Bls</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="H92" s="2" t="n">
         <v>94.7</v>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>19–171</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="L92" s="3" t="n">
+      <c r="N92" s="3" t="n">
         <v>0.4895</v>
       </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O92" s="4" t="n">
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="P92" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q92" s="2" t="inlineStr">
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R92" s="2" t="inlineStr">
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U92" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -7688,63 +8889,76 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
+          <t>Sponsorluk / özel format</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>Line Up</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="H93" s="2" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>13–165</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="L93" s="3" t="n">
+      <c r="N93" s="3" t="n">
         <v>194.58</v>
       </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>bu yayıncı, bu sektör</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O93" s="4" t="n">
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>bu yayıncı, bu sektör</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="4" t="n">
         <v>215955</v>
       </c>
-      <c r="P93" s="2" t="inlineStr">
-        <is>
-          <t>tahmin</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="inlineStr">
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>tahmin</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
         <is>
           <t>sektör + yayın türü</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr">
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>ana tür</t>
+        </is>
+      </c>
+      <c r="U93" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R93"/>
+  <autoFilter ref="A1:U93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>